--- a/Avantis Mapping/SPARQL_class.xlsx
+++ b/Avantis Mapping/SPARQL_class.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A86443-CDDB-49A6-ACCC-737FB38FAB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9ACA1C-D385-4DF1-A46D-C190F8980C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="233">
   <si>
     <t>TWONTO</t>
   </si>
@@ -101,12 +102,6 @@
     <t>Back Flow Preventer</t>
   </si>
   <si>
-    <t>Well</t>
-  </si>
-  <si>
-    <t>Man Lift</t>
-  </si>
-  <si>
     <t>Cyclone</t>
   </si>
   <si>
@@ -128,9 +123,6 @@
     <t>Computer Hardware</t>
   </si>
   <si>
-    <t>Water Trailer</t>
-  </si>
-  <si>
     <t>Server</t>
   </si>
   <si>
@@ -140,15 +132,9 @@
     <t>Condensing Unit</t>
   </si>
   <si>
-    <t>Crane</t>
-  </si>
-  <si>
     <t>Conveyor</t>
   </si>
   <si>
-    <t>First Aid</t>
-  </si>
-  <si>
     <t>Compressor</t>
   </si>
   <si>
@@ -176,9 +162,6 @@
     <t>Circuit Breaker</t>
   </si>
   <si>
-    <t>Network Switch</t>
-  </si>
-  <si>
     <t>Motor</t>
   </si>
   <si>
@@ -206,15 +189,9 @@
     <t>Engine</t>
   </si>
   <si>
-    <t>Weigh Scale</t>
-  </si>
-  <si>
     <t>Actuator</t>
   </si>
   <si>
-    <t>Maintenance Hole</t>
-  </si>
-  <si>
     <t>Recorder</t>
   </si>
   <si>
@@ -236,15 +213,9 @@
     <t>Alarm</t>
   </si>
   <si>
-    <t>Control Panel</t>
-  </si>
-  <si>
     <t>Air Exchanger Unit</t>
   </si>
   <si>
-    <t>Cable</t>
-  </si>
-  <si>
     <t>Transmitter</t>
   </si>
   <si>
@@ -266,15 +237,9 @@
     <t>Uninterruptible Power Supply</t>
   </si>
   <si>
-    <t>Generator</t>
-  </si>
-  <si>
     <t>Vacuum Cleaner</t>
   </si>
   <si>
-    <t>Starter</t>
-  </si>
-  <si>
     <t>Analyzer</t>
   </si>
   <si>
@@ -287,18 +252,12 @@
     <t>Controller</t>
   </si>
   <si>
-    <t>Network</t>
-  </si>
-  <si>
     <t>Valve</t>
   </si>
   <si>
     <t>Incinerator</t>
   </si>
   <si>
-    <t>Capacitor</t>
-  </si>
-  <si>
     <t>Chiller</t>
   </si>
   <si>
@@ -308,9 +267,6 @@
     <t>Biofilter</t>
   </si>
   <si>
-    <t>Load Break Switch</t>
-  </si>
-  <si>
     <t>Cooling Tower</t>
   </si>
   <si>
@@ -329,9 +285,6 @@
     <t>Mixer</t>
   </si>
   <si>
-    <t>Compactor</t>
-  </si>
-  <si>
     <t>Chemical Feeder</t>
   </si>
   <si>
@@ -344,9 +297,6 @@
     <t>Communications Equipment</t>
   </si>
   <si>
-    <t>Transfer Compactor</t>
-  </si>
-  <si>
     <t>Lifting Device</t>
   </si>
   <si>
@@ -378,9 +328,6 @@
   </si>
   <si>
     <t>Safety Equipment</t>
-  </si>
-  <si>
-    <t>Remote Transmission Unit</t>
   </si>
   <si>
     <t>Vent</t>
@@ -416,18 +363,12 @@
     <t>http://www.toronto.ca/TWONTO#channel_gate</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#blower</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#instrument_air_or_pneumatic_control_panel</t>
   </si>
   <si>
     <t>http://www.toronto.ca/TWONTO#UV_disinfection_assembly</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#RTU_panel</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#clarifier</t>
   </si>
   <si>
@@ -443,9 +384,6 @@
     <t>http://www.toronto.ca/TWONTO#ladder</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#lifting_device</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#air_duct_segment</t>
   </si>
   <si>
@@ -503,256 +441,310 @@
     <t>http://www.toronto.ca/TWONTO#backflow_preventer</t>
   </si>
   <si>
+    <t>http://www.toronto.ca/TWONTO#man_lift</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#tool</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#cyclone_classifier</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#gearbox</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#transformer</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#plumbing</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#ventilation_system</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#screen</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#burner_component_of_asset</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#computer</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#humidifier</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#server_appliance</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#dehumidifier</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#fire_equipment</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#conveyor</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#communication_equipment</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#compressor</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#grinder_or_comminutor</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#passenger_vehicle</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#fixed_gas_detector</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#pipette</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#PLC</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#lighting_unit</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#operator_interface_terminal</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#test_equipment</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#auto_sampler</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#system_process_control</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#classifier</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#breaker</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#motor</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#air_scrubber</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#elevator</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#storage_tank</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#security_system</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#power_washer</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#collector_mechanism</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#boat</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#granular_material</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#engine</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#actuator</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#data_logger</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#equipment_or_access_chamber</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#ejector</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#vortex_classifier</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#air_handler_unit</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#safety_equipment</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#substation</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#air_exchange_unit</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#instrument_transmitter</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#flame_arrestor</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#pipe_segment</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#heat_exchanger</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#venturi</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#UPS</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#instrument_sensor_element</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#pumping_station_assets</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#vacuum_cleaner</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#chemical_or_concentration_analyzer</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#instrument_gauge_or_display</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#still_or_video_mobile_camera</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#controller</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#valve</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#incinerator</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#pneumatic_control_system</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#chiller</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#hydraulic_system</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#filtration_tank</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#cooling_tower</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#rupture_disc</t>
+  </si>
+  <si>
+    <t>Rupture Disc</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#pump</t>
+  </si>
+  <si>
+    <t>Pump</t>
+  </si>
+  <si>
+    <t>Scissorlift</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#lifting_equipment</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#alarm</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#power_mobile_equipment</t>
+  </si>
+  <si>
+    <t>Earthmoving Equipment</t>
+  </si>
+  <si>
+    <t>Switchgear</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#blower_or_fan_with_drive</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#RPU_panel</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#crane</t>
+  </si>
+  <si>
+    <t>Crane</t>
+  </si>
+  <si>
+    <t>Operator Interface Terminal</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#generator</t>
+  </si>
+  <si>
+    <t>Generator</t>
+  </si>
+  <si>
+    <t>Man Lift</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#compactor</t>
+  </si>
+  <si>
+    <t>Compactor</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#water_trailer</t>
+  </si>
+  <si>
+    <t>Water Trailer</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#capacitor</t>
+  </si>
+  <si>
+    <t>Capacitor</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#load_break_disconnect_switch</t>
+  </si>
+  <si>
+    <t>Load Break Switch</t>
+  </si>
+  <si>
     <t>http://www.toronto.ca/TWONTO#well</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#man_lift</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#tool</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#cyclone_classifier</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#gearbox</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#transformer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#plumbing</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#ventilation_system</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#screen</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#burner_component_of_asset</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#computer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#humidifier</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#water_trailer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#server_appliance</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#dehumidifier</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#fire_equipment</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#crane</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#conveyor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#first_aid_kit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#communication_equipment</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#compressor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#grinder_or_comminutor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#passenger_vehicle</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#fixed_gas_detector</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pipette</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#PLC</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#lighting_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#operator_interface_terminal</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#compactor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#test_equipment</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#auto_sampler</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#system_process_control</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#classifier</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#breaker</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#network_switch</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#motor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_scrubber</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#elevator</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#storage_tank</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#security_system</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#power_washer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#collector_mechanism</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#boat</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#granular_material</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#engine</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#weight_scale</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#actuator</t>
+    <t>Well</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#process_control_panel</t>
+  </si>
+  <si>
+    <t>Control Panel</t>
   </si>
   <si>
     <t>http://www.toronto.ca/TWONTO#manhole</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#data_logger</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#equipment_or_access_chamber</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#ejector</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#vortex_classifier</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_handler_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#alarm_device</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#safety_equipment</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#substation</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#process_control_panel</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_exchange_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#cable_segment</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_transmitter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#flame_arrestor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pipe_segment</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#heat_exchanger</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#venturi</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#UPS</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_sensor_element</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#generator-set</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pumping_station_assets</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#vacuum_cleaner</t>
+    <t>Maintenance Hole</t>
   </si>
   <si>
     <t>http://www.toronto.ca/TWONTO#motor_starter</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#chemical_or_concentration_analyzer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_gauge_or_display</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#still_or_video_mobile_camera</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#controller</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#network_panel</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#valve</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#incinerator</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pneumatic_control_system</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#capacitor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#chiller</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#hydraulic_system</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#filtration_tank</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#load_break_disconnect_switch</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#cooling_tower</t>
+    <t>Starter</t>
   </si>
 </sst>
 </file>
@@ -790,7 +782,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -798,21 +790,83 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF4472C4"/>
+          <bgColor rgb="FF4472C4"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -851,8 +905,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}" name="Table1" displayName="Table1" ref="A2:B122" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B122" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}" name="Table1" displayName="Table1" ref="A2:B121" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="A2:B121" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:B3">
+    <sortCondition ref="B2:B3"/>
+  </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{501FC86E-2DD7-42BC-9958-D448426BC6D0}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{D1C1254F-83F0-416B-8CC1-E040F314ACEE}" name="Avantis_Class"/>
@@ -861,10 +918,24 @@
 </table>
 </file>
 
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E08C8530-6083-4465-9A8F-B94D1108CEB5}" name="Table2" displayName="Table2" ref="C3:D110" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+  <autoFilter ref="C3:D110" xr:uid="{E08C8530-6083-4465-9A8F-B94D1108CEB5}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C4:D110">
+    <sortCondition ref="D3:D110"/>
+  </sortState>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{47D62A1B-6CE8-4777-98D5-5BF71912989B}" name="TWONTO"/>
+    <tableColumn id="2" xr3:uid="{7EFDD4BA-4DF9-44C0-8ADA-C0F8ADD2A8B8}" name="Avantis_Class"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -902,7 +973,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1008,7 +1079,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1150,7 +1221,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1158,7 +1229,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B122"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="69.85546875" bestFit="1" customWidth="1"/>
@@ -1167,7 +1238,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1180,7 +1251,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
@@ -1188,775 +1259,772 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>132</v>
+        <v>199</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="B15" t="s">
-        <v>115</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="B16" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>140</v>
+        <v>201</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>202</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="B28" t="s">
-        <v>117</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="B32" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="B33" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="B34" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="B35" t="s">
-        <v>22</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="B36" t="s">
-        <v>119</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="B37" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="B40" t="s">
-        <v>112</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="B42" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="B43" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="B44" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="B45" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="B46" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="B47" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B48" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="B49" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="B50" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="B51" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="B52" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="B53" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>172</v>
+        <v>115</v>
       </c>
       <c r="B54" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="B55" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="B56" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B57" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="B58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="B59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="B60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="B61" t="s">
-        <v>120</v>
+        <v>42</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="B62" t="s">
-        <v>114</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="B63" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>180</v>
+        <v>131</v>
       </c>
       <c r="B64" t="s">
-        <v>97</v>
+        <v>203</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="B65" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="B66" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="B67" t="s">
-        <v>109</v>
+        <v>45</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="B68" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="B69" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="B70" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="B71" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="B72" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="B73" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="B74" t="s">
-        <v>111</v>
+        <v>51</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B75" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="B76" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="B77" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="B78" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="B79" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="B80" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="B81" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="B82" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="B83" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="B84" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="B85" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="B86" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="B87" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="B88" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B89" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="B90" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>205</v>
+        <v>113</v>
       </c>
       <c r="B91" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="B92" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="B93" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="B94" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="B95" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="B96" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="B97" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="B98" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>213</v>
-      </c>
-      <c r="B99" t="s">
-        <v>71</v>
+        <v>194</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="B100" t="s">
         <v>73</v>
@@ -1964,175 +2032,1049 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B101" t="s">
-        <v>74</v>
+        <v>207</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="B102" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="B103" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>218</v>
+        <v>159</v>
       </c>
       <c r="B104" t="s">
-        <v>76</v>
+        <v>208</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="B105" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>134</v>
+        <v>209</v>
       </c>
       <c r="B106" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="B107" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="B108" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>222</v>
+        <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>79</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="B110" t="s">
-        <v>80</v>
+        <v>212</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>224</v>
+        <v>154</v>
       </c>
       <c r="B111" t="s">
-        <v>81</v>
+        <v>213</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="B112" t="s">
-        <v>82</v>
+        <v>215</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>226</v>
+        <v>131</v>
       </c>
       <c r="B113" t="s">
-        <v>83</v>
+        <v>216</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="B114" t="s">
-        <v>84</v>
+        <v>218</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="B115" t="s">
-        <v>85</v>
+        <v>220</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>229</v>
+        <v>221</v>
+      </c>
+      <c r="B116" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B117" t="s">
-        <v>86</v>
+        <v>224</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B118" t="s">
-        <v>87</v>
+        <v>226</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B119" t="s">
-        <v>88</v>
+        <v>228</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B120" t="s">
-        <v>89</v>
+        <v>230</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B121" t="s">
+        <v>232</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4884BCF2-D0BF-43AF-A366-0080E3AC3682}">
+  <dimension ref="C3:D110"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="73.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>205</v>
+      </c>
+      <c r="D9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>188</v>
+      </c>
+      <c r="D10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>130</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>197</v>
+      </c>
+      <c r="D13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>209</v>
+      </c>
+      <c r="D14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>167</v>
+      </c>
+      <c r="D15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>129</v>
+      </c>
+      <c r="D16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>139</v>
+      </c>
+      <c r="D18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>190</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>172</v>
+      </c>
+      <c r="D21" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>195</v>
+      </c>
+      <c r="D23" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>158</v>
+      </c>
+      <c r="D26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>166</v>
+      </c>
+      <c r="D27" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>146</v>
+      </c>
+      <c r="D28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>140</v>
+      </c>
+      <c r="D30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>117</v>
+      </c>
+      <c r="D32" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>191</v>
+      </c>
+      <c r="D33" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>145</v>
+      </c>
+      <c r="D34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>198</v>
+      </c>
+      <c r="D35" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
+        <v>133</v>
+      </c>
+      <c r="D36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
+        <v>121</v>
+      </c>
+      <c r="D37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C38" t="s">
+        <v>143</v>
+      </c>
+      <c r="D38" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C39" t="s">
+        <v>108</v>
+      </c>
+      <c r="D39" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C40" t="s">
+        <v>125</v>
+      </c>
+      <c r="D40" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="41" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
+        <v>120</v>
+      </c>
+      <c r="D41" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C42" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C43" t="s">
+        <v>112</v>
+      </c>
+      <c r="D43" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="44" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C44" t="s">
+        <v>206</v>
+      </c>
+      <c r="D44" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="45" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C45" t="s">
+        <v>162</v>
+      </c>
+      <c r="D45" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C46" t="s">
+        <v>169</v>
+      </c>
+      <c r="D46" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C47" t="s">
+        <v>209</v>
+      </c>
+      <c r="D47" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C48" t="s">
+        <v>168</v>
+      </c>
+      <c r="D48" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C49" t="s">
+        <v>144</v>
+      </c>
+      <c r="D49" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="50" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C50" t="s">
+        <v>180</v>
+      </c>
+      <c r="D50" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C51" t="s">
+        <v>118</v>
+      </c>
+      <c r="D51" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C52" t="s">
+        <v>150</v>
+      </c>
+      <c r="D52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C53" t="s">
+        <v>104</v>
+      </c>
+      <c r="D53" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C54" t="s">
+        <v>134</v>
+      </c>
+      <c r="D54" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C55" t="s">
+        <v>148</v>
+      </c>
+      <c r="D55" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="56" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C56" t="s">
+        <v>182</v>
+      </c>
+      <c r="D56" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="57" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C57" t="s">
+        <v>109</v>
+      </c>
+      <c r="D57" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C58" t="s">
+        <v>141</v>
+      </c>
+      <c r="D58" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="59" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C59" t="s">
+        <v>137</v>
+      </c>
+      <c r="D59" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C60" t="s">
+        <v>196</v>
+      </c>
+      <c r="D60" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="61" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C61" t="s">
+        <v>193</v>
+      </c>
+      <c r="D61" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="62" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C62" t="s">
+        <v>189</v>
+      </c>
+      <c r="D62" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="63" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C63" t="s">
+        <v>173</v>
+      </c>
+      <c r="D63" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="64" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C64" t="s">
+        <v>111</v>
+      </c>
+      <c r="D64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C65" t="s">
+        <v>204</v>
+      </c>
+      <c r="D65" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="66" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C66" t="s">
+        <v>153</v>
+      </c>
+      <c r="D66" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C67" t="s">
+        <v>115</v>
+      </c>
+      <c r="D67" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="68" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C68" t="s">
+        <v>160</v>
+      </c>
+      <c r="D68" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="69" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C69" t="s">
+        <v>123</v>
+      </c>
+      <c r="D69" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C70" t="s">
+        <v>151</v>
+      </c>
+      <c r="D70" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="71" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C71" t="s">
+        <v>181</v>
+      </c>
+      <c r="D71" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="72" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C72" t="s">
+        <v>136</v>
+      </c>
+      <c r="D72" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="73" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C73" t="s">
+        <v>165</v>
+      </c>
+      <c r="D73" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="74" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C74" t="s">
+        <v>152</v>
+      </c>
+      <c r="D74" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="75" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C75" t="s">
+        <v>110</v>
+      </c>
+      <c r="D75" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C76" t="s">
+        <v>201</v>
+      </c>
+      <c r="D76" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="77" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C77" t="s">
+        <v>186</v>
+      </c>
+      <c r="D77" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="78" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C78" t="s">
+        <v>119</v>
+      </c>
+      <c r="D78" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C79" t="s">
+        <v>171</v>
+      </c>
+      <c r="D79" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="80" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C80" t="s">
+        <v>210</v>
+      </c>
+      <c r="D80" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="81" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C81" t="s">
+        <v>199</v>
+      </c>
+      <c r="D81" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="82" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C82" t="s">
+        <v>176</v>
+      </c>
+      <c r="D82" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="83" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C83" t="s">
+        <v>156</v>
+      </c>
+      <c r="D83" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="84" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C84" t="s">
+        <v>154</v>
+      </c>
+      <c r="D84" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="85" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C85" t="s">
+        <v>131</v>
+      </c>
+      <c r="D85" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="86" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C86" t="s">
+        <v>138</v>
+      </c>
+      <c r="D86" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C87" t="s">
+        <v>161</v>
+      </c>
+      <c r="D87" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="88" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C88" t="s">
+        <v>164</v>
+      </c>
+      <c r="D88" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="89" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C89" t="s">
+        <v>185</v>
+      </c>
+      <c r="D89" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="90" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C90" t="s">
+        <v>142</v>
+      </c>
+      <c r="D90" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="91" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C91" t="s">
+        <v>127</v>
+      </c>
+      <c r="D91" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="92" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C92" t="s">
+        <v>113</v>
+      </c>
+      <c r="D92" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="93" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C93" t="s">
+        <v>177</v>
+      </c>
+      <c r="D93" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>235</v>
-      </c>
-      <c r="B122" t="s">
-        <v>91</v>
+    <row r="94" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C94" t="s">
+        <v>159</v>
+      </c>
+      <c r="D94" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="95" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C95" t="s">
+        <v>157</v>
+      </c>
+      <c r="D95" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="96" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C96" t="s">
+        <v>163</v>
+      </c>
+      <c r="D96" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="97" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C97" t="s">
+        <v>155</v>
+      </c>
+      <c r="D97" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="98" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C98" t="s">
+        <v>132</v>
+      </c>
+      <c r="D98" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="99" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C99" t="s">
+        <v>135</v>
+      </c>
+      <c r="D99" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="100" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C100" t="s">
+        <v>179</v>
+      </c>
+      <c r="D100" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="101" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C101" t="s">
+        <v>106</v>
+      </c>
+      <c r="D101" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C102" t="s">
+        <v>184</v>
+      </c>
+      <c r="D102" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="103" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C103" t="s">
+        <v>187</v>
+      </c>
+      <c r="D103" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="104" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C104" t="s">
+        <v>192</v>
+      </c>
+      <c r="D104" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="105" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C105" t="s">
+        <v>116</v>
+      </c>
+      <c r="D105" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="106" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C106" t="s">
+        <v>149</v>
+      </c>
+      <c r="D106" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="107" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C107" t="s">
+        <v>112</v>
+      </c>
+      <c r="D107" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="108" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C108" t="s">
+        <v>183</v>
+      </c>
+      <c r="D108" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="109" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C109" t="s">
+        <v>174</v>
+      </c>
+      <c r="D109" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="110" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C110" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_class.xlsx
+++ b/Avantis Mapping/SPARQL_class.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9ACA1C-D385-4DF1-A46D-C190F8980C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCAAEC70-EC44-4659-87F8-055AABA5EC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="239">
   <si>
     <t>TWONTO</t>
   </si>
@@ -745,6 +745,24 @@
   </si>
   <si>
     <t>Starter</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#blower</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#fuel_burning_heater</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#network_panel</t>
+  </si>
+  <si>
+    <t>Network</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#air_silencer</t>
+  </si>
+  <si>
+    <t>Silencer</t>
   </si>
 </sst>
 </file>
@@ -905,8 +923,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}" name="Table1" displayName="Table1" ref="A2:B121" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="A2:B121" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}" name="Table1" displayName="Table1" ref="A2:B123" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="A2:B123" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:B3">
     <sortCondition ref="B2:B3"/>
   </sortState>
@@ -1229,7 +1247,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B121"/>
+  <dimension ref="A1:B123"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="69.85546875" bestFit="1" customWidth="1"/>
@@ -1259,943 +1277,959 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>233</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>109</v>
+        <v>233</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>234</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>199</v>
+        <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>200</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>118</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>201</v>
+        <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>202</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>201</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>202</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B27" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B30" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B31" t="s">
-        <v>101</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B32" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B33" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>135</v>
+        <v>225</v>
       </c>
       <c r="B34" t="s">
-        <v>23</v>
+        <v>226</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B35" t="s">
-        <v>95</v>
+        <v>216</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B39" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B42" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B43" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B44" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B45" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>147</v>
+        <v>219</v>
       </c>
       <c r="B46" t="s">
-        <v>32</v>
+        <v>220</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B47" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B48" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B49" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>151</v>
+        <v>211</v>
       </c>
       <c r="B50" t="s">
-        <v>35</v>
+        <v>212</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="B51" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B52" t="s">
-        <v>37</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B53" t="s">
-        <v>102</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>115</v>
+        <v>148</v>
       </c>
       <c r="B54" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B55" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B56" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B57" t="s">
-        <v>92</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B58" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B59" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B60" t="s">
-        <v>41</v>
+        <v>102</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="B61" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
       <c r="B62" t="s">
-        <v>43</v>
+        <v>218</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>112</v>
+        <v>155</v>
       </c>
       <c r="B63" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="B64" t="s">
-        <v>203</v>
+        <v>38</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B65" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B66" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B67" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B68" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="B69" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B70" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>168</v>
+        <v>112</v>
       </c>
       <c r="B71" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="B72" t="s">
-        <v>49</v>
+        <v>203</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B73" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B74" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B75" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B76" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="B77" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>175</v>
+        <v>214</v>
       </c>
       <c r="B78" t="s">
-        <v>56</v>
+        <v>215</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="B79" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B80" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="B81" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B82" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>179</v>
+        <v>229</v>
       </c>
       <c r="B83" t="s">
-        <v>59</v>
+        <v>230</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="B84" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B85" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B86" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="B87" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="B88" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="B89" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B90" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>113</v>
+        <v>177</v>
       </c>
       <c r="B91" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>187</v>
+        <v>227</v>
       </c>
       <c r="B92" t="s">
-        <v>66</v>
+        <v>228</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="B93" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="B94" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="B95" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="B96" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="B97" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B98" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>194</v>
+        <v>183</v>
+      </c>
+      <c r="B99" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="B100" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="B101" t="s">
-        <v>207</v>
+        <v>62</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>196</v>
+        <v>154</v>
       </c>
       <c r="B102" t="s">
-        <v>74</v>
+        <v>213</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="B103" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="B104" t="s">
-        <v>208</v>
+        <v>98</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="B105" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="B106" t="s">
-        <v>79</v>
+        <v>232</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="B107" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="B108" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="B109" t="s">
-        <v>8</v>
+        <v>69</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="B110" t="s">
-        <v>212</v>
+        <v>70</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>154</v>
+        <v>235</v>
       </c>
       <c r="B111" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="B112" t="s">
-        <v>215</v>
+        <v>71</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>131</v>
+        <v>193</v>
       </c>
       <c r="B113" t="s">
-        <v>216</v>
+        <v>72</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>217</v>
-      </c>
-      <c r="B114" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B115" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="B116" t="s">
-        <v>222</v>
+        <v>73</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="B117" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
       <c r="B118" t="s">
-        <v>226</v>
+        <v>74</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>227</v>
+        <v>197</v>
       </c>
       <c r="B119" t="s">
-        <v>228</v>
+        <v>75</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B120" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>231</v>
+        <v>159</v>
       </c>
       <c r="B121" t="s">
-        <v>232</v>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>198</v>
+      </c>
+      <c r="B122" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>237</v>
+      </c>
+      <c r="B123" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_class.xlsx
+++ b/Avantis Mapping/SPARQL_class.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCAAEC70-EC44-4659-87F8-055AABA5EC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1EC3E0-1B2B-4F29-AEB8-8B1AE883ACB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="251">
   <si>
     <t>TWONTO</t>
   </si>
@@ -750,9 +750,6 @@
     <t>http://www.toronto.ca/TWONTO#blower</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#fuel_burning_heater</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#network_panel</t>
   </si>
   <si>
@@ -763,6 +760,45 @@
   </si>
   <si>
     <t>Silencer</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#venturi_flow_sensor_element</t>
+  </si>
+  <si>
+    <t>Remote Transmission Unit</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#network_switch</t>
+  </si>
+  <si>
+    <t>Network Switch</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#burner_-_component_of_asset</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#flowmeter</t>
+  </si>
+  <si>
+    <t>Meter</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#weight_scale</t>
+  </si>
+  <si>
+    <t>Weigh Scale</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#process_controller</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#cable_segment</t>
+  </si>
+  <si>
+    <t>Electrical Power Line</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#equipment_chamber_or_access_chamber</t>
   </si>
 </sst>
 </file>
@@ -923,8 +959,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}" name="Table1" displayName="Table1" ref="A2:B123" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="A2:B123" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}" name="Table1" displayName="Table1" ref="A2:B126" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="A2:B126" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:B3">
     <sortCondition ref="B2:B3"/>
   </sortState>
@@ -1247,19 +1283,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B123"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B126"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="69.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="69.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="165" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1267,7 +1303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>104</v>
       </c>
@@ -1275,7 +1311,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>233</v>
       </c>
@@ -1283,7 +1319,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>105</v>
       </c>
@@ -1291,7 +1327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>106</v>
       </c>
@@ -1299,7 +1335,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>107</v>
       </c>
@@ -1307,7 +1343,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>233</v>
       </c>
@@ -1315,23 +1351,23 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>234</v>
+        <v>108</v>
       </c>
       <c r="B9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>108</v>
-      </c>
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>110</v>
       </c>
@@ -1339,7 +1375,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>111</v>
       </c>
@@ -1347,7 +1383,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>112</v>
       </c>
@@ -1355,7 +1391,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>113</v>
       </c>
@@ -1363,7 +1399,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>114</v>
       </c>
@@ -1371,7 +1407,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>115</v>
       </c>
@@ -1379,7 +1415,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>199</v>
       </c>
@@ -1387,7 +1423,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>116</v>
       </c>
@@ -1395,7 +1431,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>117</v>
       </c>
@@ -1403,7 +1439,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>118</v>
       </c>
@@ -1411,7 +1447,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>119</v>
       </c>
@@ -1419,7 +1455,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>120</v>
       </c>
@@ -1427,7 +1463,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>121</v>
       </c>
@@ -1435,7 +1471,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>122</v>
       </c>
@@ -1443,7 +1479,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>201</v>
       </c>
@@ -1451,7 +1487,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>123</v>
       </c>
@@ -1459,7 +1495,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>124</v>
       </c>
@@ -1467,7 +1503,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>125</v>
       </c>
@@ -1475,7 +1511,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>126</v>
       </c>
@@ -1483,7 +1519,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>127</v>
       </c>
@@ -1491,7 +1527,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>128</v>
       </c>
@@ -1499,7 +1535,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>129</v>
       </c>
@@ -1507,7 +1543,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>130</v>
       </c>
@@ -1515,7 +1551,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>225</v>
       </c>
@@ -1523,7 +1559,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>131</v>
       </c>
@@ -1531,7 +1567,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>132</v>
       </c>
@@ -1539,7 +1575,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>133</v>
       </c>
@@ -1547,7 +1583,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>134</v>
       </c>
@@ -1555,47 +1591,47 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
+        <v>238</v>
+      </c>
+      <c r="B39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>135</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>136</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>137</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B42" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
         <v>138</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B43" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>139</v>
-      </c>
-      <c r="B43" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>140</v>
       </c>
@@ -1603,7 +1639,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>141</v>
       </c>
@@ -1611,7 +1647,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>219</v>
       </c>
@@ -1619,7 +1655,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>142</v>
       </c>
@@ -1627,7 +1663,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>143</v>
       </c>
@@ -1635,601 +1671,625 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
+        <v>210</v>
+      </c>
+      <c r="B49" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>144</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B50" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>211</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B51" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>145</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B52" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>146</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B53" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>147</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B54" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>148</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B55" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
         <v>149</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
         <v>150</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B57" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>151</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B58" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
         <v>152</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B59" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>153</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B60" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>154</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B61" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>115</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B62" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>217</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B63" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>155</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B64" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
         <v>156</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B65" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
         <v>157</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B66" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
         <v>158</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B67" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
         <v>159</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B68" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>240</v>
+      </c>
+      <c r="B69" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
         <v>160</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B70" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
         <v>161</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B71" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
         <v>162</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B72" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
         <v>112</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B73" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>131</v>
-      </c>
-      <c r="B72" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
         <v>163</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B74" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>242</v>
+      </c>
+      <c r="B75" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
         <v>164</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B76" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>243</v>
+      </c>
+      <c r="B77" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
         <v>165</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B78" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
         <v>166</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B79" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
         <v>204</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B80" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
         <v>214</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B81" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
         <v>167</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B82" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
         <v>168</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B83" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
         <v>169</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B84" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>245</v>
+      </c>
+      <c r="B85" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
         <v>170</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B86" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
         <v>229</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B87" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
         <v>171</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B88" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>172</v>
-      </c>
-      <c r="B85" t="s">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>173</v>
+      </c>
+      <c r="B89" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>174</v>
+      </c>
+      <c r="B90" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>210</v>
+      </c>
+      <c r="B91" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>175</v>
+      </c>
+      <c r="B92" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>176</v>
+      </c>
+      <c r="B93" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>177</v>
+      </c>
+      <c r="B94" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>227</v>
+      </c>
+      <c r="B95" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>205</v>
+      </c>
+      <c r="B96" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>178</v>
+      </c>
+      <c r="B97" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>179</v>
+      </c>
+      <c r="B98" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>180</v>
+      </c>
+      <c r="B99" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>181</v>
+      </c>
+      <c r="B100" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>182</v>
+      </c>
+      <c r="B101" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>184</v>
+      </c>
+      <c r="B102" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>185</v>
+      </c>
+      <c r="B103" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>247</v>
+      </c>
+      <c r="B104" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>154</v>
+      </c>
+      <c r="B105" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>186</v>
+      </c>
+      <c r="B106" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>113</v>
+      </c>
+      <c r="B107" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>187</v>
+      </c>
+      <c r="B108" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>236</v>
+      </c>
+      <c r="B109" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>231</v>
+      </c>
+      <c r="B110" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>188</v>
+      </c>
+      <c r="B111" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>248</v>
+      </c>
+      <c r="B112" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>189</v>
+      </c>
+      <c r="B113" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>190</v>
+      </c>
+      <c r="B114" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>234</v>
+      </c>
+      <c r="B115" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>192</v>
+      </c>
+      <c r="B116" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>193</v>
+      </c>
+      <c r="B117" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>221</v>
+      </c>
+      <c r="B119" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>195</v>
+      </c>
+      <c r="B120" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>196</v>
+      </c>
+      <c r="B121" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>197</v>
+      </c>
+      <c r="B122" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>223</v>
+      </c>
+      <c r="B123" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>159</v>
+      </c>
+      <c r="B124" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>250</v>
+      </c>
+      <c r="B125" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>173</v>
-      </c>
-      <c r="B86" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>174</v>
-      </c>
-      <c r="B87" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>210</v>
-      </c>
-      <c r="B88" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>175</v>
-      </c>
-      <c r="B89" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>176</v>
-      </c>
-      <c r="B90" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>177</v>
-      </c>
-      <c r="B91" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>227</v>
-      </c>
-      <c r="B92" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>205</v>
-      </c>
-      <c r="B93" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>178</v>
-      </c>
-      <c r="B94" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>179</v>
-      </c>
-      <c r="B95" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>180</v>
-      </c>
-      <c r="B96" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>181</v>
-      </c>
-      <c r="B97" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>182</v>
-      </c>
-      <c r="B98" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>183</v>
-      </c>
-      <c r="B99" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>184</v>
-      </c>
-      <c r="B100" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>185</v>
-      </c>
-      <c r="B101" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>154</v>
-      </c>
-      <c r="B102" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>186</v>
-      </c>
-      <c r="B103" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>113</v>
-      </c>
-      <c r="B104" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>187</v>
-      </c>
-      <c r="B105" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>231</v>
-      </c>
-      <c r="B106" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>188</v>
-      </c>
-      <c r="B107" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>189</v>
-      </c>
-      <c r="B108" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>190</v>
-      </c>
-      <c r="B109" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>191</v>
-      </c>
-      <c r="B110" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>235</v>
-      </c>
-      <c r="B111" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>192</v>
-      </c>
-      <c r="B112" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>193</v>
-      </c>
-      <c r="B113" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>221</v>
-      </c>
-      <c r="B115" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>195</v>
-      </c>
-      <c r="B116" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>206</v>
-      </c>
-      <c r="B117" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>196</v>
-      </c>
-      <c r="B118" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>197</v>
-      </c>
-      <c r="B119" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>223</v>
-      </c>
-      <c r="B120" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>159</v>
-      </c>
-      <c r="B121" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
         <v>198</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B126" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>237</v>
-      </c>
-      <c r="B123" t="s">
-        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -2244,13 +2304,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4884BCF2-D0BF-43AF-A366-0080E3AC3682}">
   <dimension ref="C3:D110"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="73.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="3" max="3" width="73.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -2258,7 +2318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
         <v>170</v>
       </c>
@@ -2266,7 +2326,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
         <v>115</v>
       </c>
@@ -2274,7 +2334,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
         <v>178</v>
       </c>
@@ -2282,7 +2342,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C7" t="s">
         <v>175</v>
       </c>
@@ -2290,7 +2350,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
         <v>105</v>
       </c>
@@ -2298,7 +2358,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C9" t="s">
         <v>205</v>
       </c>
@@ -2306,7 +2366,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C10" t="s">
         <v>188</v>
       </c>
@@ -2314,7 +2374,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C11" t="s">
         <v>130</v>
       </c>
@@ -2322,7 +2382,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
         <v>126</v>
       </c>
@@ -2330,7 +2390,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C13" t="s">
         <v>197</v>
       </c>
@@ -2338,7 +2398,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
         <v>209</v>
       </c>
@@ -2346,7 +2406,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C15" t="s">
         <v>167</v>
       </c>
@@ -2354,7 +2414,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C16" t="s">
         <v>129</v>
       </c>
@@ -2362,7 +2422,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C17" t="s">
         <v>113</v>
       </c>
@@ -2370,7 +2430,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C18" t="s">
         <v>139</v>
       </c>
@@ -2378,7 +2438,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C19" t="s">
         <v>190</v>
       </c>
@@ -2386,7 +2446,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C20" t="s">
         <v>124</v>
       </c>
@@ -2394,7 +2454,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C21" t="s">
         <v>172</v>
       </c>
@@ -2402,7 +2462,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C22" t="s">
         <v>122</v>
       </c>
@@ -2410,7 +2470,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C23" t="s">
         <v>195</v>
       </c>
@@ -2418,7 +2478,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C24" t="s">
         <v>159</v>
       </c>
@@ -2426,7 +2486,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C25" t="s">
         <v>107</v>
       </c>
@@ -2434,7 +2494,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C26" t="s">
         <v>158</v>
       </c>
@@ -2442,7 +2502,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C27" t="s">
         <v>166</v>
       </c>
@@ -2450,7 +2510,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C28" t="s">
         <v>146</v>
       </c>
@@ -2458,7 +2518,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C29" t="s">
         <v>147</v>
       </c>
@@ -2466,7 +2526,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C30" t="s">
         <v>140</v>
       </c>
@@ -2474,7 +2534,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C31" t="s">
         <v>128</v>
       </c>
@@ -2482,7 +2542,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C32" t="s">
         <v>117</v>
       </c>
@@ -2490,7 +2550,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C33" t="s">
         <v>191</v>
       </c>
@@ -2498,7 +2558,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C34" t="s">
         <v>145</v>
       </c>
@@ -2506,7 +2566,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C35" t="s">
         <v>198</v>
       </c>
@@ -2514,7 +2574,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C36" t="s">
         <v>133</v>
       </c>
@@ -2522,7 +2582,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C37" t="s">
         <v>121</v>
       </c>
@@ -2530,7 +2590,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C38" t="s">
         <v>143</v>
       </c>
@@ -2538,7 +2598,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C39" t="s">
         <v>108</v>
       </c>
@@ -2546,7 +2606,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C40" t="s">
         <v>125</v>
       </c>
@@ -2554,7 +2614,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="41" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C41" t="s">
         <v>120</v>
       </c>
@@ -2562,7 +2622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C42" t="s">
         <v>114</v>
       </c>
@@ -2570,7 +2630,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C43" t="s">
         <v>112</v>
       </c>
@@ -2578,7 +2638,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="44" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C44" t="s">
         <v>206</v>
       </c>
@@ -2586,7 +2646,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="45" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C45" t="s">
         <v>162</v>
       </c>
@@ -2594,7 +2654,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C46" t="s">
         <v>169</v>
       </c>
@@ -2602,7 +2662,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="47" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C47" t="s">
         <v>209</v>
       </c>
@@ -2610,7 +2670,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="48" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C48" t="s">
         <v>168</v>
       </c>
@@ -2618,7 +2678,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C49" t="s">
         <v>144</v>
       </c>
@@ -2626,7 +2686,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C50" t="s">
         <v>180</v>
       </c>
@@ -2634,7 +2694,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C51" t="s">
         <v>118</v>
       </c>
@@ -2642,7 +2702,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C52" t="s">
         <v>150</v>
       </c>
@@ -2650,7 +2710,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C53" t="s">
         <v>104</v>
       </c>
@@ -2658,7 +2718,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C54" t="s">
         <v>134</v>
       </c>
@@ -2666,7 +2726,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C55" t="s">
         <v>148</v>
       </c>
@@ -2674,7 +2734,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="56" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C56" t="s">
         <v>182</v>
       </c>
@@ -2682,7 +2742,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="57" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C57" t="s">
         <v>109</v>
       </c>
@@ -2690,7 +2750,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C58" t="s">
         <v>141</v>
       </c>
@@ -2698,7 +2758,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="59" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C59" t="s">
         <v>137</v>
       </c>
@@ -2706,7 +2766,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C60" t="s">
         <v>196</v>
       </c>
@@ -2714,7 +2774,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="61" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C61" t="s">
         <v>193</v>
       </c>
@@ -2722,7 +2782,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="62" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C62" t="s">
         <v>189</v>
       </c>
@@ -2730,7 +2790,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="63" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C63" t="s">
         <v>173</v>
       </c>
@@ -2738,7 +2798,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="64" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C64" t="s">
         <v>111</v>
       </c>
@@ -2746,7 +2806,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C65" t="s">
         <v>204</v>
       </c>
@@ -2754,7 +2814,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C66" t="s">
         <v>153</v>
       </c>
@@ -2762,7 +2822,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="67" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C67" t="s">
         <v>115</v>
       </c>
@@ -2770,7 +2830,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C68" t="s">
         <v>160</v>
       </c>
@@ -2778,7 +2838,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="69" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C69" t="s">
         <v>123</v>
       </c>
@@ -2786,7 +2846,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="70" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C70" t="s">
         <v>151</v>
       </c>
@@ -2794,7 +2854,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="71" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C71" t="s">
         <v>181</v>
       </c>
@@ -2802,7 +2862,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="72" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C72" t="s">
         <v>136</v>
       </c>
@@ -2810,7 +2870,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="73" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C73" t="s">
         <v>165</v>
       </c>
@@ -2818,7 +2878,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="74" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C74" t="s">
         <v>152</v>
       </c>
@@ -2826,7 +2886,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="75" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C75" t="s">
         <v>110</v>
       </c>
@@ -2834,7 +2894,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C76" t="s">
         <v>201</v>
       </c>
@@ -2842,7 +2902,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="77" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C77" t="s">
         <v>186</v>
       </c>
@@ -2850,7 +2910,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="78" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C78" t="s">
         <v>119</v>
       </c>
@@ -2858,7 +2918,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="79" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C79" t="s">
         <v>171</v>
       </c>
@@ -2866,7 +2926,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="80" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C80" t="s">
         <v>210</v>
       </c>
@@ -2874,7 +2934,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="81" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C81" t="s">
         <v>199</v>
       </c>
@@ -2882,7 +2942,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C82" t="s">
         <v>176</v>
       </c>
@@ -2890,7 +2950,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="83" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C83" t="s">
         <v>156</v>
       </c>
@@ -2898,7 +2958,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="84" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C84" t="s">
         <v>154</v>
       </c>
@@ -2906,7 +2966,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="85" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C85" t="s">
         <v>131</v>
       </c>
@@ -2914,7 +2974,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="86" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C86" t="s">
         <v>138</v>
       </c>
@@ -2922,7 +2982,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="87" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C87" t="s">
         <v>161</v>
       </c>
@@ -2930,7 +2990,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="88" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C88" t="s">
         <v>164</v>
       </c>
@@ -2938,7 +2998,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="89" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C89" t="s">
         <v>185</v>
       </c>
@@ -2946,7 +3006,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="90" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C90" t="s">
         <v>142</v>
       </c>
@@ -2954,7 +3014,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C91" t="s">
         <v>127</v>
       </c>
@@ -2962,7 +3022,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C92" t="s">
         <v>113</v>
       </c>
@@ -2970,7 +3030,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="93" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C93" t="s">
         <v>177</v>
       </c>
@@ -2978,7 +3038,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="94" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C94" t="s">
         <v>159</v>
       </c>
@@ -2986,7 +3046,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="95" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C95" t="s">
         <v>157</v>
       </c>
@@ -2994,7 +3054,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="96" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C96" t="s">
         <v>163</v>
       </c>
@@ -3002,7 +3062,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="97" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C97" t="s">
         <v>155</v>
       </c>
@@ -3010,7 +3070,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="98" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C98" t="s">
         <v>132</v>
       </c>
@@ -3018,7 +3078,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="99" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C99" t="s">
         <v>135</v>
       </c>
@@ -3026,7 +3086,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="100" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C100" t="s">
         <v>179</v>
       </c>
@@ -3034,7 +3094,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="101" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C101" t="s">
         <v>106</v>
       </c>
@@ -3042,7 +3102,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C102" t="s">
         <v>184</v>
       </c>
@@ -3050,7 +3110,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="103" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C103" t="s">
         <v>187</v>
       </c>
@@ -3058,7 +3118,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="104" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C104" t="s">
         <v>192</v>
       </c>
@@ -3066,7 +3126,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="105" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C105" t="s">
         <v>116</v>
       </c>
@@ -3074,7 +3134,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="106" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C106" t="s">
         <v>149</v>
       </c>
@@ -3082,7 +3142,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C107" t="s">
         <v>112</v>
       </c>
@@ -3090,7 +3150,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="108" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C108" t="s">
         <v>183</v>
       </c>
@@ -3098,7 +3158,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="109" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C109" t="s">
         <v>174</v>
       </c>
@@ -3106,7 +3166,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="110" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C110" t="s">
         <v>194</v>
       </c>

--- a/Avantis Mapping/SPARQL_class.xlsx
+++ b/Avantis Mapping/SPARQL_class.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C74F9A36-D5F3-4988-B991-714A476AE663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F6DA356-5B87-4439-8ECB-4034E5824258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10360" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="238">
   <si>
     <t>TWONTO</t>
   </si>
@@ -317,391 +317,436 @@
     <t>SCADA computer terminal</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#channel_gate</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_air_or_pneumatic_control_panel</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#UV_disinfection_assembly</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#clarifier</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#controlled_door_access</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#heater</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#protection_relay</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#ladder</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_duct_segment</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#building</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#mixer_or_agitator</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#VFD</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#quencher</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#dryer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_damper</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#outfall_or_discharge_point</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#centrifuge</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#drain</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#battery</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#strainer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#AC_condenser_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#boiler</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#backflow_preventer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#man_lift</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#tool</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#cyclone_classifier</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#gearbox</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#transformer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#ventilation_system</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#screen</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#computer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#humidifier</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#server_appliance</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#dehumidifier</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#conveyor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#compressor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#grinder_or_comminutor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#passenger_vehicle</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#fixed_gas_detector</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pipette</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#PLC</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#lighting_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#operator_interface_terminal</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#auto_sampler</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#classifier</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#breaker</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#motor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_scrubber</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#elevator</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#storage_tank</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#security_system</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#power_washer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#collector_mechanism</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#boat</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#granular_material</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#engine</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#actuator</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#data_logger</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#ejector</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#vortex_classifier</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_handler_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#substation</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_exchange_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_transmitter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#flame_arrestor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pipe_segment</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#heat_exchanger</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#UPS</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_sensor_element</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pumping_station_assets</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#vacuum_cleaner</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#chemical_or_concentration_analyzer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_gauge_or_display</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#still_or_video_mobile_camera</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#valve</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#incinerator</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pneumatic_control_system</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#chiller</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#hydraulic_system</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#filtration_tank</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#cooling_tower</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#rupture_disc</t>
-  </si>
-  <si>
-    <t>Rupture Disc</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pump</t>
-  </si>
-  <si>
-    <t>Pump</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#lifting_equipment</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#alarm</t>
-  </si>
-  <si>
-    <t>Switchgear</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#RPU_panel</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#crane</t>
-  </si>
-  <si>
     <t>Crane</t>
   </si>
   <si>
-    <t>Operator Interface Terminal</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#generator</t>
-  </si>
-  <si>
     <t>Generator</t>
   </si>
   <si>
     <t>Man Lift</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#compactor</t>
-  </si>
-  <si>
     <t>Compactor</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#water_trailer</t>
-  </si>
-  <si>
     <t>Water Trailer</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#capacitor</t>
-  </si>
-  <si>
     <t>Capacitor</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#load_break_disconnect_switch</t>
-  </si>
-  <si>
     <t>Load Break Switch</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#well</t>
-  </si>
-  <si>
     <t>Well</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#process_control_panel</t>
-  </si>
-  <si>
     <t>Control Panel</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#manhole</t>
-  </si>
-  <si>
     <t>Maintenance Hole</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#motor_starter</t>
-  </si>
-  <si>
     <t>Starter</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#blower</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#network_panel</t>
-  </si>
-  <si>
     <t>Network</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#air_silencer</t>
-  </si>
-  <si>
-    <t>Silencer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#venturi_flow_sensor_element</t>
-  </si>
-  <si>
     <t>Remote Transmission Unit</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#network_switch</t>
-  </si>
-  <si>
     <t>Network Switch</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#burner_-_component_of_asset</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#flowmeter</t>
-  </si>
-  <si>
-    <t>Meter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#weight_scale</t>
-  </si>
-  <si>
     <t>Weigh Scale</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#process_controller</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#cable_segment</t>
-  </si>
-  <si>
-    <t>Electrical Power Line</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#equipment_chamber_or_access_chamber</t>
+    <t>construction or earthmoving machine</t>
+  </si>
+  <si>
+    <t>Earthmoving Equipment</t>
+  </si>
+  <si>
+    <t>auto sampler</t>
+  </si>
+  <si>
+    <t>boat</t>
+  </si>
+  <si>
+    <t>burner - component of asset</t>
+  </si>
+  <si>
+    <t>building</t>
+  </si>
+  <si>
+    <t>passenger vehicle</t>
+  </si>
+  <si>
+    <t>still or video mobile camera</t>
+  </si>
+  <si>
+    <t>instrument transmitter</t>
+  </si>
+  <si>
+    <t>network panel</t>
+  </si>
+  <si>
+    <t>network switch</t>
+  </si>
+  <si>
+    <t>crane</t>
+  </si>
+  <si>
+    <t>VFD</t>
+  </si>
+  <si>
+    <t>boiler</t>
+  </si>
+  <si>
+    <t>instrument gauge or display</t>
+  </si>
+  <si>
+    <t>air scrubber</t>
+  </si>
+  <si>
+    <t>substation</t>
+  </si>
+  <si>
+    <t>mixer or agitator</t>
+  </si>
+  <si>
+    <t>controlled door access</t>
+  </si>
+  <si>
+    <t>vacuum cleaner</t>
+  </si>
+  <si>
+    <t>battery</t>
+  </si>
+  <si>
+    <t>granular material</t>
+  </si>
+  <si>
+    <t>elevator</t>
+  </si>
+  <si>
+    <t>portable chlorine analyzer</t>
+  </si>
+  <si>
+    <t>Chlorine Monitoring Device,Por</t>
+  </si>
+  <si>
+    <t>energy recovery wheel</t>
+  </si>
+  <si>
+    <t>Energy Wheel</t>
+  </si>
+  <si>
+    <t>leachate monitor</t>
+  </si>
+  <si>
+    <t>Leachate Monitoring</t>
+  </si>
+  <si>
+    <t>groundskeeping equipment</t>
+  </si>
+  <si>
+    <t>groundskeeping_equipment</t>
+  </si>
+  <si>
+    <t>operator interface terminal</t>
+  </si>
+  <si>
+    <t>incinerator</t>
+  </si>
+  <si>
+    <t>air duct segment</t>
+  </si>
+  <si>
+    <t>compressor</t>
+  </si>
+  <si>
+    <t>pumping station assets</t>
+  </si>
+  <si>
+    <t>evaporator</t>
+  </si>
+  <si>
+    <t>Evaporator</t>
+  </si>
+  <si>
+    <t>drain</t>
+  </si>
+  <si>
+    <t>generator</t>
+  </si>
+  <si>
+    <t>well</t>
+  </si>
+  <si>
+    <t>weight scale</t>
+  </si>
+  <si>
+    <t>motor starter</t>
+  </si>
+  <si>
+    <t>power washer</t>
+  </si>
+  <si>
+    <t>hydraulic system</t>
+  </si>
+  <si>
+    <t>heat exchanger</t>
+  </si>
+  <si>
+    <t>capacitor</t>
+  </si>
+  <si>
+    <t>venturi flow sensor element</t>
+  </si>
+  <si>
+    <t>pipette</t>
+  </si>
+  <si>
+    <t>security system</t>
+  </si>
+  <si>
+    <t>heater</t>
+  </si>
+  <si>
+    <t>humidifier</t>
+  </si>
+  <si>
+    <t>PLC</t>
+  </si>
+  <si>
+    <t>flame arrestor</t>
+  </si>
+  <si>
+    <t>ladder</t>
+  </si>
+  <si>
+    <t>air exchange unit</t>
+  </si>
+  <si>
+    <t>condenser</t>
+  </si>
+  <si>
+    <t>air damper</t>
+  </si>
+  <si>
+    <t>blower</t>
+  </si>
+  <si>
+    <t>process control panel</t>
+  </si>
+  <si>
+    <t>valve</t>
+  </si>
+  <si>
+    <t>lighting unit</t>
+  </si>
+  <si>
+    <t>strainer</t>
+  </si>
+  <si>
+    <t>centrifuge</t>
+  </si>
+  <si>
+    <t>first aid equipment</t>
+  </si>
+  <si>
+    <t>First Aid</t>
+  </si>
+  <si>
+    <t>dehumidifier</t>
+  </si>
+  <si>
+    <t>alarm</t>
+  </si>
+  <si>
+    <t>compactor</t>
+  </si>
+  <si>
+    <t>ejector</t>
+  </si>
+  <si>
+    <t>equipment chamber or access chamber</t>
+  </si>
+  <si>
+    <t>channel gate</t>
+  </si>
+  <si>
+    <t>backflow preventer</t>
+  </si>
+  <si>
+    <t>filtration tank</t>
+  </si>
+  <si>
+    <t>manhole</t>
+  </si>
+  <si>
+    <t>DC power supply</t>
+  </si>
+  <si>
+    <t>Power Supply Unit</t>
+  </si>
+  <si>
+    <t>instrument sensor element</t>
+  </si>
+  <si>
+    <t>outfall or discharge point</t>
+  </si>
+  <si>
+    <t>load break disconnect switch</t>
+  </si>
+  <si>
+    <t>fixed gas detector</t>
+  </si>
+  <si>
+    <t>lifting device</t>
+  </si>
+  <si>
+    <t>process controller</t>
+  </si>
+  <si>
+    <t>man lift</t>
+  </si>
+  <si>
+    <t>gearbox</t>
+  </si>
+  <si>
+    <t>data logger</t>
+  </si>
+  <si>
+    <t>collector mechanism</t>
+  </si>
+  <si>
+    <t>chemical or concentration analyzer</t>
+  </si>
+  <si>
+    <t>cooling tower</t>
+  </si>
+  <si>
+    <t>air handler unit</t>
+  </si>
+  <si>
+    <t>chiller</t>
+  </si>
+  <si>
+    <t>lifting device component</t>
+  </si>
+  <si>
+    <t>Rigging Equipment</t>
+  </si>
+  <si>
+    <t>protection relay</t>
+  </si>
+  <si>
+    <t>ventilation system</t>
+  </si>
+  <si>
+    <t>grinder or comminutor</t>
+  </si>
+  <si>
+    <t>classifier</t>
+  </si>
+  <si>
+    <t>cable segment</t>
+  </si>
+  <si>
+    <t>Cable</t>
+  </si>
+  <si>
+    <t>storage tank</t>
+  </si>
+  <si>
+    <t>motor</t>
+  </si>
+  <si>
+    <t>actuator</t>
+  </si>
+  <si>
+    <t>conveyor</t>
+  </si>
+  <si>
+    <t>dryer</t>
+  </si>
+  <si>
+    <t>pipe segment</t>
+  </si>
+  <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>water trailer</t>
+  </si>
+  <si>
+    <t>leveler</t>
+  </si>
+  <si>
+    <t>Leveller</t>
+  </si>
+  <si>
+    <t>Transfer Compactor</t>
+  </si>
+  <si>
+    <t>RPU panel</t>
+  </si>
+  <si>
+    <t>first aid kit</t>
+  </si>
+  <si>
+    <t>instrument air or pneumatic control panel</t>
+  </si>
+  <si>
+    <t>UV disinfection assembly</t>
+  </si>
+  <si>
+    <t>screen</t>
+  </si>
+  <si>
+    <t>clarifier</t>
+  </si>
+  <si>
+    <t>quencher</t>
+  </si>
+  <si>
+    <t>engine</t>
+  </si>
+  <si>
+    <t>tool</t>
+  </si>
+  <si>
+    <t>vortex classifier</t>
+  </si>
+  <si>
+    <t>cyclone classifier</t>
+  </si>
+  <si>
+    <t>network router</t>
+  </si>
+  <si>
+    <t>Router</t>
+  </si>
+  <si>
+    <t>roof</t>
+  </si>
+  <si>
+    <t>Roof</t>
+  </si>
+  <si>
+    <t>computer</t>
+  </si>
+  <si>
+    <t>transformer</t>
+  </si>
+  <si>
+    <t>server appliance</t>
+  </si>
+  <si>
+    <t>breaker</t>
   </si>
   <si>
     <t>PREFIX rdf: &lt;http://www.w3.org/1999/02/22-rdf-syntax-ns#&gt;
@@ -709,9 +754,10 @@
 PREFIX rdfs: &lt;http://www.w3.org/2000/01/rdf-schema#&gt;
 PREFIX xsd: &lt;http://www.w3.org/2001/XMLSchema#&gt;
 PREFIX tw: &lt;http://www.toronto.ca/TWONTO#&gt;
-SELECT ?TWONTO (STR(?object) as ?Avantis)
+SELECT (STR(?TWONTO_Label) AS ?Label) (STR(?object) AS ?Avantis)
 WHERE { 
     ?TWONTO tw:is_equivalent_to_Avantis_class ?object .
+    ?TWONTO rdfs:label ?TWONTO_Label .
     FILTER NOT EXISTS { ?TWONTO owl:deprecated "true"^^xsd:boolean }
 }</t>
   </si>
@@ -812,8 +858,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}" name="Table1" displayName="Table1" ref="A2:B116" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B116" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}" name="Table1" displayName="Table1" ref="A2:B125" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B125" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:B3">
     <sortCondition ref="B2:B3"/>
   </sortState>
@@ -1122,16 +1168,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B116"/>
+  <dimension ref="A1:B125"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="69.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="174" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1144,911 +1190,986 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>204</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>204</v>
+        <v>114</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="B16" t="s">
-        <v>175</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="B21" t="s">
-        <v>177</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>196</v>
+        <v>140</v>
       </c>
       <c r="B30" t="s">
-        <v>197</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="B31" t="s">
-        <v>187</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="B34" t="s">
-        <v>22</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>209</v>
+        <v>146</v>
       </c>
       <c r="B35" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="B36" t="s">
-        <v>23</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="B39" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="B41" t="s">
-        <v>191</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="B42" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="B43" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="B44" t="s">
-        <v>210</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>182</v>
+        <v>113</v>
       </c>
       <c r="B45" t="s">
-        <v>183</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="B46" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="B47" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="B48" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="B49" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="B50" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="B51" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="B52" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="B53" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="B54" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="B55" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="B56" t="s">
-        <v>189</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="B57" t="s">
-        <v>38</v>
+        <v>101</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="B58" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="B59" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>211</v>
+        <v>169</v>
       </c>
       <c r="B60" t="s">
-        <v>212</v>
+        <v>37</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="B61" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="B62" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="B63" t="s">
-        <v>43</v>
+        <v>173</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>101</v>
+        <v>174</v>
       </c>
       <c r="B64" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="B65" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>213</v>
+        <v>176</v>
       </c>
       <c r="B66" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="B67" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>214</v>
+        <v>178</v>
       </c>
       <c r="B68" t="s">
-        <v>215</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="B69" t="s">
-        <v>45</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="B70" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B71" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B72" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="B73" t="s">
-        <v>47</v>
+        <v>184</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>147</v>
+        <v>185</v>
       </c>
       <c r="B74" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="B75" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>216</v>
+        <v>141</v>
       </c>
       <c r="B76" t="s">
-        <v>217</v>
+        <v>87</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="B77" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="B78" t="s">
-        <v>201</v>
+        <v>34</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>150</v>
+        <v>189</v>
       </c>
       <c r="B79" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="B80" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="B81" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="B82" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>153</v>
+        <v>193</v>
       </c>
       <c r="B83" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>154</v>
+        <v>194</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B85" t="s">
-        <v>199</v>
+        <v>67</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="B86" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>155</v>
+        <v>197</v>
       </c>
       <c r="B87" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="B88" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>157</v>
+        <v>199</v>
       </c>
       <c r="B89" t="s">
-        <v>60</v>
+        <v>200</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>158</v>
+        <v>201</v>
       </c>
       <c r="B90" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>159</v>
+        <v>202</v>
       </c>
       <c r="B91" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="B92" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>161</v>
+        <v>204</v>
       </c>
       <c r="B93" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="B94" t="s">
-        <v>70</v>
+        <v>206</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>135</v>
+        <v>207</v>
       </c>
       <c r="B95" t="s">
-        <v>184</v>
+        <v>44</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>162</v>
+        <v>208</v>
       </c>
       <c r="B96" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>102</v>
+        <v>208</v>
       </c>
       <c r="B97" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>163</v>
+        <v>209</v>
       </c>
       <c r="B98" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B99" t="s">
-        <v>208</v>
+        <v>31</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B100" t="s">
-        <v>203</v>
+        <v>13</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B101" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="B102" t="s">
-        <v>220</v>
+        <v>61</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>165</v>
+        <v>213</v>
       </c>
       <c r="B103" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>166</v>
+        <v>214</v>
       </c>
       <c r="B104" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="B105" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B106" t="s">
-        <v>71</v>
+        <v>217</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>168</v>
+        <v>218</v>
       </c>
       <c r="B107" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>169</v>
+        <v>219</v>
+      </c>
+      <c r="B108" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="B109" t="s">
-        <v>193</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>170</v>
+        <v>125</v>
       </c>
       <c r="B110" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>171</v>
+        <v>221</v>
       </c>
       <c r="B111" t="s">
-        <v>74</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>172</v>
+        <v>222</v>
       </c>
       <c r="B112" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="B113" t="s">
-        <v>195</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>138</v>
+        <v>224</v>
       </c>
       <c r="B114" t="s">
-        <v>180</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B115" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>173</v>
+        <v>226</v>
       </c>
       <c r="B116" t="s">
-        <v>76</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>227</v>
+      </c>
+      <c r="B117" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>228</v>
+      </c>
+      <c r="B118" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>229</v>
+      </c>
+      <c r="B119" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>231</v>
+      </c>
+      <c r="B120" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>233</v>
+      </c>
+      <c r="B121" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>234</v>
+      </c>
+      <c r="B122" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>235</v>
+      </c>
+      <c r="B123" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>236</v>
+      </c>
+      <c r="B124" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>218</v>
+      </c>
+      <c r="B125" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_class.xlsx
+++ b/Avantis Mapping/SPARQL_class.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F6DA356-5B87-4439-8ECB-4034E5824258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF17061-BEB7-4638-BF49-997AB6F2C7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="238">
   <si>
     <t>TWONTO</t>
   </si>
@@ -362,391 +362,391 @@
     <t>Weigh Scale</t>
   </si>
   <si>
-    <t>construction or earthmoving machine</t>
-  </si>
-  <si>
     <t>Earthmoving Equipment</t>
   </si>
   <si>
-    <t>auto sampler</t>
-  </si>
-  <si>
-    <t>boat</t>
-  </si>
-  <si>
-    <t>burner - component of asset</t>
-  </si>
-  <si>
-    <t>building</t>
-  </si>
-  <si>
-    <t>passenger vehicle</t>
-  </si>
-  <si>
-    <t>still or video mobile camera</t>
-  </si>
-  <si>
-    <t>instrument transmitter</t>
-  </si>
-  <si>
-    <t>network panel</t>
-  </si>
-  <si>
-    <t>network switch</t>
-  </si>
-  <si>
-    <t>crane</t>
-  </si>
-  <si>
-    <t>VFD</t>
-  </si>
-  <si>
-    <t>boiler</t>
-  </si>
-  <si>
-    <t>instrument gauge or display</t>
-  </si>
-  <si>
-    <t>air scrubber</t>
-  </si>
-  <si>
-    <t>substation</t>
-  </si>
-  <si>
-    <t>mixer or agitator</t>
-  </si>
-  <si>
-    <t>controlled door access</t>
-  </si>
-  <si>
-    <t>vacuum cleaner</t>
-  </si>
-  <si>
-    <t>battery</t>
-  </si>
-  <si>
-    <t>granular material</t>
-  </si>
-  <si>
-    <t>elevator</t>
-  </si>
-  <si>
-    <t>portable chlorine analyzer</t>
-  </si>
-  <si>
     <t>Chlorine Monitoring Device,Por</t>
   </si>
   <si>
-    <t>energy recovery wheel</t>
-  </si>
-  <si>
     <t>Energy Wheel</t>
   </si>
   <si>
-    <t>leachate monitor</t>
-  </si>
-  <si>
     <t>Leachate Monitoring</t>
   </si>
   <si>
-    <t>groundskeeping equipment</t>
-  </si>
-  <si>
     <t>groundskeeping_equipment</t>
   </si>
   <si>
-    <t>operator interface terminal</t>
-  </si>
-  <si>
-    <t>incinerator</t>
-  </si>
-  <si>
-    <t>air duct segment</t>
-  </si>
-  <si>
-    <t>compressor</t>
-  </si>
-  <si>
-    <t>pumping station assets</t>
-  </si>
-  <si>
-    <t>evaporator</t>
-  </si>
-  <si>
     <t>Evaporator</t>
   </si>
   <si>
-    <t>drain</t>
-  </si>
-  <si>
-    <t>generator</t>
-  </si>
-  <si>
-    <t>well</t>
-  </si>
-  <si>
-    <t>weight scale</t>
-  </si>
-  <si>
-    <t>motor starter</t>
-  </si>
-  <si>
-    <t>power washer</t>
-  </si>
-  <si>
-    <t>hydraulic system</t>
-  </si>
-  <si>
-    <t>heat exchanger</t>
-  </si>
-  <si>
-    <t>capacitor</t>
-  </si>
-  <si>
-    <t>venturi flow sensor element</t>
-  </si>
-  <si>
-    <t>pipette</t>
-  </si>
-  <si>
-    <t>security system</t>
-  </si>
-  <si>
-    <t>heater</t>
-  </si>
-  <si>
-    <t>humidifier</t>
-  </si>
-  <si>
-    <t>PLC</t>
-  </si>
-  <si>
-    <t>flame arrestor</t>
-  </si>
-  <si>
-    <t>ladder</t>
-  </si>
-  <si>
-    <t>air exchange unit</t>
-  </si>
-  <si>
-    <t>condenser</t>
-  </si>
-  <si>
-    <t>air damper</t>
-  </si>
-  <si>
-    <t>blower</t>
-  </si>
-  <si>
-    <t>process control panel</t>
-  </si>
-  <si>
-    <t>valve</t>
-  </si>
-  <si>
-    <t>lighting unit</t>
-  </si>
-  <si>
-    <t>strainer</t>
-  </si>
-  <si>
-    <t>centrifuge</t>
-  </si>
-  <si>
-    <t>first aid equipment</t>
-  </si>
-  <si>
     <t>First Aid</t>
   </si>
   <si>
-    <t>dehumidifier</t>
-  </si>
-  <si>
-    <t>alarm</t>
-  </si>
-  <si>
-    <t>compactor</t>
-  </si>
-  <si>
-    <t>ejector</t>
-  </si>
-  <si>
-    <t>equipment chamber or access chamber</t>
-  </si>
-  <si>
-    <t>channel gate</t>
-  </si>
-  <si>
-    <t>backflow preventer</t>
-  </si>
-  <si>
-    <t>filtration tank</t>
-  </si>
-  <si>
-    <t>manhole</t>
-  </si>
-  <si>
-    <t>DC power supply</t>
-  </si>
-  <si>
     <t>Power Supply Unit</t>
   </si>
   <si>
-    <t>instrument sensor element</t>
-  </si>
-  <si>
-    <t>outfall or discharge point</t>
-  </si>
-  <si>
-    <t>load break disconnect switch</t>
-  </si>
-  <si>
-    <t>fixed gas detector</t>
-  </si>
-  <si>
-    <t>lifting device</t>
-  </si>
-  <si>
-    <t>process controller</t>
-  </si>
-  <si>
-    <t>man lift</t>
-  </si>
-  <si>
-    <t>gearbox</t>
-  </si>
-  <si>
-    <t>data logger</t>
-  </si>
-  <si>
-    <t>collector mechanism</t>
-  </si>
-  <si>
-    <t>chemical or concentration analyzer</t>
-  </si>
-  <si>
-    <t>cooling tower</t>
-  </si>
-  <si>
-    <t>air handler unit</t>
-  </si>
-  <si>
-    <t>chiller</t>
-  </si>
-  <si>
-    <t>lifting device component</t>
-  </si>
-  <si>
     <t>Rigging Equipment</t>
   </si>
   <si>
-    <t>protection relay</t>
-  </si>
-  <si>
-    <t>ventilation system</t>
-  </si>
-  <si>
-    <t>grinder or comminutor</t>
-  </si>
-  <si>
-    <t>classifier</t>
-  </si>
-  <si>
-    <t>cable segment</t>
-  </si>
-  <si>
     <t>Cable</t>
   </si>
   <si>
-    <t>storage tank</t>
-  </si>
-  <si>
-    <t>motor</t>
-  </si>
-  <si>
-    <t>actuator</t>
-  </si>
-  <si>
-    <t>conveyor</t>
-  </si>
-  <si>
-    <t>dryer</t>
-  </si>
-  <si>
-    <t>pipe segment</t>
-  </si>
-  <si>
-    <t>UPS</t>
-  </si>
-  <si>
-    <t>water trailer</t>
-  </si>
-  <si>
-    <t>leveler</t>
-  </si>
-  <si>
     <t>Leveller</t>
   </si>
   <si>
     <t>Transfer Compactor</t>
   </si>
   <si>
-    <t>RPU panel</t>
-  </si>
-  <si>
-    <t>first aid kit</t>
-  </si>
-  <si>
-    <t>instrument air or pneumatic control panel</t>
-  </si>
-  <si>
-    <t>UV disinfection assembly</t>
-  </si>
-  <si>
-    <t>screen</t>
-  </si>
-  <si>
-    <t>clarifier</t>
-  </si>
-  <si>
-    <t>quencher</t>
-  </si>
-  <si>
-    <t>engine</t>
-  </si>
-  <si>
-    <t>tool</t>
-  </si>
-  <si>
-    <t>vortex classifier</t>
-  </si>
-  <si>
-    <t>cyclone classifier</t>
-  </si>
-  <si>
-    <t>network router</t>
-  </si>
-  <si>
     <t>Router</t>
   </si>
   <si>
-    <t>roof</t>
-  </si>
-  <si>
     <t>Roof</t>
   </si>
   <si>
-    <t>computer</t>
-  </si>
-  <si>
-    <t>transformer</t>
-  </si>
-  <si>
-    <t>server appliance</t>
-  </si>
-  <si>
-    <t>breaker</t>
+    <t>http://www.toronto.ca/TWONTO#00122</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00186</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00680</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00755</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00234</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00650</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00538</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00253</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00794</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00316</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00747</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00633</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00219</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00665</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00126</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00526</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00443</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00355</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00232</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00468</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00802</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00124</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00569</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00179</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00291</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00245</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00138</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00531</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00708</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00192</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00220</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00405</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00787</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00622</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00475</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00213</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00147</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00246</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00208</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00226</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00255</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00396</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00492</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00614</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00474</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00359</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00487</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00144</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00551</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00446</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00105</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00493</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00348</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00165</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00202</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00318</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00294</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00151</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00263</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00354</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00200</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00710</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00478</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00781</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00613</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00142</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00236</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00145</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00457</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00361</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00119</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00429</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00418</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00570</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00673</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00189</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00789</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00194</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00416</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00434</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00628</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00321</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00288</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00397</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00811</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00806</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00532</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00596</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00435</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00233</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00548</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00408</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00462</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00315</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00402</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00306</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00581</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00780</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00167</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00244</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00183</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00445</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00148</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00714</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00128</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00537</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00539</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00251</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00447</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00706</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00559</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00191</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00181</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00163</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00238</t>
   </si>
   <si>
     <t>PREFIX rdf: &lt;http://www.w3.org/1999/02/22-rdf-syntax-ns#&gt;
@@ -754,11 +754,10 @@
 PREFIX rdfs: &lt;http://www.w3.org/2000/01/rdf-schema#&gt;
 PREFIX xsd: &lt;http://www.w3.org/2001/XMLSchema#&gt;
 PREFIX tw: &lt;http://www.toronto.ca/TWONTO#&gt;
-SELECT (STR(?TWONTO_Label) AS ?Label) (STR(?object) AS ?Avantis)
+SELECT (STR(?sub) AS ?TWONTO) (STR(?object) AS ?Avantis)
 WHERE { 
-    ?TWONTO tw:is_equivalent_to_Avantis_class ?object .
-    ?TWONTO rdfs:label ?TWONTO_Label .
-    FILTER NOT EXISTS { ?TWONTO owl:deprecated "true"^^xsd:boolean }
+    ?sub tw:is_equivalent_to_Avantis_class ?object .
+    FILTER NOT EXISTS { ?sub owl:deprecated "true"^^xsd:boolean }
 }</t>
   </si>
 </sst>
@@ -858,8 +857,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}" name="Table1" displayName="Table1" ref="A2:B125" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B125" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}" name="Table1" displayName="Table1" ref="A2:B123" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B123" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:B3">
     <sortCondition ref="B2:B3"/>
   </sortState>
@@ -1168,14 +1167,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B125"/>
+  <dimension ref="A1:B123"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="69.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="174" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>237</v>
       </c>
@@ -1190,986 +1189,970 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="B3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="B12" t="s">
-        <v>106</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="B20" t="s">
-        <v>6</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B25" t="s">
-        <v>132</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="B26" t="s">
-        <v>134</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="B27" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B28" t="s">
-        <v>138</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B33" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B34" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B35" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B36" t="s">
-        <v>94</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B38" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B39" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B40" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B41" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B42" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="B43" t="s">
-        <v>98</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B44" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="B45" t="s">
-        <v>89</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B46" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B47" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B48" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B50" t="s">
-        <v>36</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B51" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B52" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B53" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="B54" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B55" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B56" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B57" t="s">
-        <v>101</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B58" t="s">
-        <v>71</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B59" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="B60" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="B61" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B62" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B63" t="s">
-        <v>173</v>
+        <v>29</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B64" t="s">
-        <v>29</v>
+        <v>114</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B65" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B66" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B67" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B68" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B69" t="s">
-        <v>2</v>
+        <v>101</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="B70" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B71" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B72" t="s">
-        <v>102</v>
+        <v>30</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B73" t="s">
-        <v>184</v>
+        <v>58</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B74" t="s">
-        <v>62</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B75" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>141</v>
+        <v>192</v>
       </c>
       <c r="B76" t="s">
-        <v>87</v>
+        <v>36</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B77" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B78" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B79" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B80" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B81" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B82" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B83" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B84" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B85" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B86" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B87" t="s">
-        <v>56</v>
+        <v>113</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B88" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B89" t="s">
-        <v>200</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B90" t="s">
-        <v>8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B91" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B92" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B93" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B94" t="s">
-        <v>206</v>
+        <v>72</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>207</v>
+        <v>169</v>
       </c>
       <c r="B95" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B96" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B97" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B98" t="s">
-        <v>50</v>
+        <v>112</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B99" t="s">
-        <v>31</v>
+        <v>111</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B100" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>166</v>
+        <v>216</v>
       </c>
       <c r="B101" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B102" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B103" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B104" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B105" t="s">
-        <v>216</v>
+        <v>17</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>176</v>
+        <v>137</v>
       </c>
       <c r="B106" t="s">
-        <v>217</v>
+        <v>79</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B107" t="s">
-        <v>86</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B108" t="s">
-        <v>173</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B109" t="s">
-        <v>3</v>
+        <v>68</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>125</v>
+        <v>224</v>
       </c>
       <c r="B110" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B111" t="s">
-        <v>4</v>
+        <v>84</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B112" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B113" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B114" t="s">
-        <v>12</v>
+        <v>106</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B115" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B116" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B117" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B118" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="B119" t="s">
-        <v>230</v>
+        <v>83</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B120" t="s">
-        <v>232</v>
+        <v>26</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B121" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B122" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B123" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
-        <v>236</v>
-      </c>
-      <c r="B124" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
-        <v>218</v>
-      </c>
-      <c r="B125" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_class.xlsx
+++ b/Avantis Mapping/SPARQL_class.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF17061-BEB7-4638-BF49-997AB6F2C7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D4C155-79E7-4B20-B76E-76F3A9BDD2A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="240">
   <si>
     <t>TWONTO</t>
   </si>
@@ -759,6 +759,12 @@
     ?sub tw:is_equivalent_to_Avantis_class ?object .
     FILTER NOT EXISTS { ?sub owl:deprecated "true"^^xsd:boolean }
 }</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00920</t>
+  </si>
+  <si>
+    <t>Office Equipment</t>
   </si>
 </sst>
 </file>
@@ -857,8 +863,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}" name="Table1" displayName="Table1" ref="A2:B123" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B123" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}" name="Table1" displayName="Table1" ref="A2:B124" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B124" xr:uid="{2F59859A-FBE4-49A6-B6BA-B68B6E359698}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:B3">
     <sortCondition ref="B2:B3"/>
   </sortState>
@@ -1167,7 +1173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B123"/>
+  <dimension ref="A1:B124"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="69.81640625" bestFit="1" customWidth="1"/>
@@ -1965,193 +1971,201 @@
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="B100" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B101" t="s">
-        <v>48</v>
+        <v>110</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B102" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B103" t="s">
-        <v>109</v>
+        <v>43</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B104" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B105" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>137</v>
+        <v>220</v>
       </c>
       <c r="B106" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>221</v>
+        <v>137</v>
       </c>
       <c r="B107" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B108" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B109" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B110" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B111" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B112" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B113" t="s">
-        <v>104</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B114" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B115" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B116" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B117" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B118" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>197</v>
+        <v>232</v>
       </c>
       <c r="B119" t="s">
-        <v>83</v>
+        <v>10</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
       <c r="B120" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B121" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B122" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
+        <v>235</v>
+      </c>
+      <c r="B123" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
         <v>236</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B124" t="s">
         <v>108</v>
       </c>
     </row>
